--- a/data/trans_dic/P15-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,62</t>
+          <t>6,5; 10,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,58</t>
+          <t>6,53; 10,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,17</t>
+          <t>4,47; 8,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,47</t>
+          <t>5,18; 9,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,01</t>
+          <t>3,63; 7,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,13</t>
+          <t>5,82; 10,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 9,38</t>
+          <t>5,59; 9,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,01</t>
+          <t>4,99; 7,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,2</t>
+          <t>5,61; 8,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 9,55</t>
+          <t>6,61; 9,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,1</t>
+          <t>5,46; 8,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,22</t>
+          <t>5,61; 8,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,97</t>
+          <t>6,98; 10,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,92</t>
+          <t>6,32; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,62</t>
+          <t>4,5; 7,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,99</t>
+          <t>2,76; 7,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,86</t>
+          <t>4,73; 7,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,26</t>
+          <t>5,64; 9,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,15</t>
+          <t>3,37; 6,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,76</t>
+          <t>4,55; 7,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,75</t>
+          <t>6,29; 8,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,84</t>
+          <t>6,43; 8,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,3</t>
+          <t>4,34; 6,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,26</t>
+          <t>3,89; 7,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,08</t>
+          <t>4,87; 9,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,83</t>
+          <t>6,0; 10,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,57</t>
+          <t>3,42; 6,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,86</t>
+          <t>2,72; 5,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,87</t>
+          <t>3,66; 6,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,71</t>
+          <t>5,72; 9,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,63</t>
+          <t>2,75; 5,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,81</t>
+          <t>2,24; 6,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,3</t>
+          <t>4,74; 7,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,04</t>
+          <t>6,25; 8,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,58</t>
+          <t>3,37; 5,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,58</t>
+          <t>2,98; 5,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,52</t>
+          <t>4,46; 7,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,47</t>
+          <t>7,75; 11,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,16</t>
+          <t>5,01; 8,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,23</t>
+          <t>4,78; 8,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,0</t>
+          <t>3,28; 5,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,72</t>
+          <t>5,51; 8,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,73</t>
+          <t>4,6; 7,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,78</t>
+          <t>4,89; 7,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,2</t>
+          <t>4,22; 6,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,83; 9,4</t>
+          <t>6,92; 9,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,49</t>
+          <t>5,18; 7,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 7,51</t>
+          <t>5,32; 7,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,33</t>
+          <t>6,48; 8,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,43</t>
+          <t>7,45; 9,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,7</t>
+          <t>5,14; 6,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,87</t>
+          <t>4,44; 6,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,11</t>
+          <t>4,5; 6,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,16</t>
+          <t>6,47; 8,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,2</t>
+          <t>4,62; 6,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,79</t>
+          <t>4,72; 6,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,93</t>
+          <t>5,74; 7,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,48</t>
+          <t>7,08; 8,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,22</t>
+          <t>5,12; 6,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,49</t>
+          <t>4,95; 6,47</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43512; 73705</t>
+          <t>45087; 73874</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46634; 74449</t>
+          <t>45911; 74422</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30703; 55103</t>
+          <t>30149; 55135</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32903; 60162</t>
+          <t>32898; 59971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26118; 48272</t>
+          <t>24980; 48522</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40256; 70644</t>
+          <t>40578; 70800</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36065; 63113</t>
+          <t>37602; 65541</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35948; 54143</t>
+          <t>33696; 53910</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74919; 113350</t>
+          <t>77513; 114544</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>93995; 133799</t>
+          <t>92566; 133754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72952; 109117</t>
+          <t>73528; 109672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74161; 107718</t>
+          <t>73527; 107434</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68046; 105488</t>
+          <t>67180; 103271</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64407; 100968</t>
+          <t>64299; 100731</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45968; 77954</t>
+          <t>45988; 76885</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33844; 95301</t>
+          <t>32890; 95332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45141; 76092</t>
+          <t>45846; 75734</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60862; 95608</t>
+          <t>58206; 94104</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36123; 64156</t>
+          <t>35137; 63961</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45025; 74367</t>
+          <t>43587; 72973</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>119598; 168816</t>
+          <t>121352; 168693</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130739; 181297</t>
+          <t>131820; 183900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90513; 130116</t>
+          <t>89577; 131548</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87340; 156259</t>
+          <t>83624; 157115</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34118; 61619</t>
+          <t>33022; 62262</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45698; 74458</t>
+          <t>45459; 75762</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25732; 49869</t>
+          <t>25985; 50670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20149; 41295</t>
+          <t>19181; 40861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24379; 47014</t>
+          <t>25004; 47222</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44553; 75465</t>
+          <t>44454; 73721</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21572; 44207</t>
+          <t>21556; 45283</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23828; 63580</t>
+          <t>20940; 63013</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63139; 99498</t>
+          <t>64634; 98512</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96397; 138816</t>
+          <t>95988; 136574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52014; 86231</t>
+          <t>52063; 86356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46207; 91390</t>
+          <t>48889; 94430</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42803; 70845</t>
+          <t>42026; 71702</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72822; 108713</t>
+          <t>73408; 108103</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45845; 76484</t>
+          <t>47011; 78267</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45282; 76256</t>
+          <t>44314; 76077</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33788; 62345</t>
+          <t>34046; 61409</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56211; 91721</t>
+          <t>57915; 90304</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47617; 80684</t>
+          <t>48004; 81212</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54162; 85214</t>
+          <t>53516; 85220</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82676; 122853</t>
+          <t>83572; 122611</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>136562; 187871</t>
+          <t>138295; 189204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102384; 148439</t>
+          <t>102675; 148786</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>105226; 151761</t>
+          <t>107521; 150533</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>213412; 272920</t>
+          <t>212290; 275280</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>254257; 323070</t>
+          <t>255444; 320308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172348; 227456</t>
+          <t>174325; 228532</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156189; 237795</t>
+          <t>153650; 236555</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>151081; 206321</t>
+          <t>151993; 204526</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>226504; 290278</t>
+          <t>230061; 294681</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>166967; 219653</t>
+          <t>163810; 219660</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>177727; 248580</t>
+          <t>172841; 242043</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>379017; 461354</t>
+          <t>381713; 466311</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>498305; 592513</t>
+          <t>494687; 591726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>354579; 431587</t>
+          <t>355480; 430098</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>354667; 462516</t>
+          <t>352614; 461129</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,64</t>
+          <t>6,5; 10,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,58</t>
+          <t>6,36; 10,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,17</t>
+          <t>4,59; 8,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,44</t>
+          <t>5,47; 9,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,05</t>
+          <t>3,78; 7,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,16</t>
+          <t>5,75; 10,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,74</t>
+          <t>5,16; 9,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,98</t>
+          <t>5,03; 7,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,29</t>
+          <t>5,4; 8,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 9,55</t>
+          <t>6,65; 9,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,14</t>
+          <t>5,48; 8,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,19</t>
+          <t>5,71; 8,16</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,74</t>
+          <t>7,0; 10,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,9</t>
+          <t>6,25; 9,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,52</t>
+          <t>4,57; 7,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,99</t>
+          <t>5,47; 9,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,82</t>
+          <t>4,54; 7,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,12</t>
+          <t>5,87; 8,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,13</t>
+          <t>3,42; 6,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,62</t>
+          <t>4,54; 7,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,74</t>
+          <t>6,26; 8,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,97</t>
+          <t>6,41; 8,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,37</t>
+          <t>4,37; 6,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,3</t>
+          <t>5,33; 7,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,18</t>
+          <t>5,0; 9,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,0</t>
+          <t>5,96; 9,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,67</t>
+          <t>3,52; 6,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,8</t>
+          <t>2,77; 5,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,91</t>
+          <t>3,62; 7,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,49</t>
+          <t>5,63; 9,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,77</t>
+          <t>2,59; 5,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,75</t>
+          <t>4,82; 7,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,23</t>
+          <t>4,7; 7,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,9</t>
+          <t>6,35; 9,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,59</t>
+          <t>3,42; 5,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,76</t>
+          <t>4,03; 6,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,61</t>
+          <t>4,52; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,41</t>
+          <t>7,62; 11,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,35</t>
+          <t>4,95; 8,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,21</t>
+          <t>4,83; 8,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,91</t>
+          <t>3,28; 5,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,58</t>
+          <t>5,41; 8,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,78</t>
+          <t>4,57; 7,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,78</t>
+          <t>5,27; 7,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,19</t>
+          <t>4,23; 6,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 9,46</t>
+          <t>6,9; 9,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,51</t>
+          <t>5,19; 7,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,45</t>
+          <t>5,53; 7,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,4</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,35</t>
+          <t>7,41; 9,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,73</t>
+          <t>5,05; 6,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,84</t>
+          <t>5,39; 7,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,05</t>
+          <t>4,49; 6,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,28</t>
+          <t>6,34; 8,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,2</t>
+          <t>4,67; 6,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,61</t>
+          <t>5,56; 6,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,01</t>
+          <t>5,66; 6,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,47</t>
+          <t>7,15; 8,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 6,2</t>
+          <t>5,1; 6,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,47</t>
+          <t>5,71; 6,88</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45087; 73874</t>
+          <t>45101; 72578</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45911; 74422</t>
+          <t>44749; 73406</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30149; 55135</t>
+          <t>30970; 54298</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32898; 59971</t>
+          <t>37816; 67051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24980; 48522</t>
+          <t>26010; 48831</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40578; 70800</t>
+          <t>40098; 70257</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37602; 65541</t>
+          <t>34706; 64270</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33696; 53910</t>
+          <t>36840; 58148</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77513; 114544</t>
+          <t>74602; 112243</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92566; 133754</t>
+          <t>93170; 132527</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73528; 109672</t>
+          <t>73788; 110902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73527; 107434</t>
+          <t>81358; 116136</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57234</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>137618</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67180; 103271</t>
+          <t>67334; 102608</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64299; 100731</t>
+          <t>63619; 101700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45988; 76885</t>
+          <t>46754; 78778</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32890; 95332</t>
+          <t>57341; 96898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45846; 75734</t>
+          <t>43952; 75622</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58206; 94104</t>
+          <t>60634; 92571</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35137; 63961</t>
+          <t>35644; 63921</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43587; 72973</t>
+          <t>48648; 79022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>121352; 168693</t>
+          <t>120843; 169632</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131820; 183900</t>
+          <t>131342; 181648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89577; 131548</t>
+          <t>90305; 132470</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83624; 157115</t>
+          <t>113075; 164723</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82453</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33022; 62262</t>
+          <t>33904; 62657</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45459; 75762</t>
+          <t>45135; 74870</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25985; 50670</t>
+          <t>26706; 49567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19181; 40861</t>
+          <t>22248; 46218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25004; 47222</t>
+          <t>24750; 48182</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44454; 73721</t>
+          <t>43751; 73380</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21556; 45283</t>
+          <t>20317; 44012</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20940; 63013</t>
+          <t>39120; 62672</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64634; 98512</t>
+          <t>64079; 100496</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95988; 136574</t>
+          <t>97471; 139391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52063; 86356</t>
+          <t>52842; 86124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48889; 94430</t>
+          <t>65038; 99197</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42026; 71702</t>
+          <t>42575; 71098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73408; 108103</t>
+          <t>72239; 108417</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47011; 78267</t>
+          <t>46403; 76656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44314; 76077</t>
+          <t>47833; 81087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34046; 61409</t>
+          <t>34033; 59905</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57915; 90304</t>
+          <t>56927; 88856</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48004; 81212</t>
+          <t>47697; 81024</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53516; 85220</t>
+          <t>58933; 87421</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83572; 122611</t>
+          <t>83694; 123918</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138295; 189204</t>
+          <t>137899; 186855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102675; 148786</t>
+          <t>102915; 149238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107521; 150533</t>
+          <t>116558; 157799</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>212290; 275280</t>
+          <t>215378; 275818</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>255444; 320308</t>
+          <t>253974; 325624</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>174325; 228532</t>
+          <t>171341; 229041</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153650; 236555</t>
+          <t>190405; 255818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>151993; 204526</t>
+          <t>151737; 203313</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>230061; 294681</t>
+          <t>225598; 290532</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>163810; 219660</t>
+          <t>165479; 222649</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>172841; 242043</t>
+          <t>207634; 261005</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>381713; 466311</t>
+          <t>376930; 462125</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>494687; 591726</t>
+          <t>499453; 596415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>355480; 430098</t>
+          <t>353845; 430711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>352614; 461129</t>
+          <t>414681; 500325</t>
         </is>
       </c>
     </row>
